--- a/data/trans_orig/P36B02_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36B02_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253063</t>
+          <t>252368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>267538</t>
+          <t>267193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241906</t>
+          <t>241543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>255034</t>
+          <t>254923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>499606</t>
+          <t>499835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>519226</t>
+          <t>519321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19947</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>14527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>417545</t>
+          <t>418870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>448305</t>
+          <t>447534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>438212</t>
+          <t>437707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>465325</t>
+          <t>465478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>866471</t>
+          <t>864402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904703</t>
+          <t>905010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44770</t>
+          <t>45541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75530</t>
+          <t>74205</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65737</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92321</t>
+          <t>92014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130553</t>
+          <t>132622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>291415</t>
+          <t>291263</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>309411</t>
+          <t>309576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>316081</t>
+          <t>316772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>329983</t>
+          <t>330000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>614951</t>
+          <t>614148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>636598</t>
+          <t>636342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27431</t>
+          <t>27583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>325583</t>
+          <t>325080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>344574</t>
+          <t>345327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350312</t>
+          <t>350967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364906</t>
+          <t>364696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>683208</t>
+          <t>682330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>706217</t>
+          <t>706305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21144</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46919</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176472</t>
+          <t>175799</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192761</t>
+          <t>192755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190551</t>
+          <t>190840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204661</t>
+          <t>203779</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373649</t>
+          <t>373737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394602</t>
+          <t>395086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>16828</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>246452</t>
+          <t>246600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261294</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253806</t>
+          <t>254152</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>269165</t>
+          <t>269239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>507322</t>
+          <t>505832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>528293</t>
+          <t>527848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24338</t>
+          <t>23992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20662</t>
+          <t>21107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566429</t>
+          <t>568304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>591534</t>
+          <t>592125</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>571237</t>
+          <t>571000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>599172</t>
+          <t>598859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1149570</t>
+          <t>1147661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1185258</t>
+          <t>1185759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23493</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48598</t>
+          <t>46723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66856</t>
+          <t>66355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102544</t>
+          <t>104453</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>672269</t>
+          <t>671678</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>699875</t>
+          <t>699598</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>737773</t>
+          <t>738804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>759673</t>
+          <t>760329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1417921</t>
+          <t>1418820</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1455643</t>
+          <t>1454943</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>43315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>71235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45738</t>
+          <t>44707</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>70781</t>
+          <t>71481</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108503</t>
+          <t>107604</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3010865</t>
+          <t>3011724</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3070960</t>
+          <t>3071974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3157344</t>
+          <t>3159450</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3209454</t>
+          <t>3214503</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6182195</t>
+          <t>6188622</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6267216</t>
+          <t>6266671</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,18%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>204701</t>
+          <t>203687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>264796</t>
+          <t>263937</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>168611</t>
+          <t>163562</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>220721</t>
+          <t>218615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>386510</t>
+          <t>387055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>471531</t>
+          <t>465104</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226907</t>
+          <t>227074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>253110</t>
+          <t>254583</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241821</t>
+          <t>242571</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264813</t>
+          <t>264923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>476124</t>
+          <t>477838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>512126</t>
+          <t>514938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>40155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67831</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69857</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105859</t>
+          <t>104145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>428231</t>
+          <t>429214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>458605</t>
+          <t>459723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>457910</t>
+          <t>459100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>486999</t>
+          <t>487240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899450</t>
+          <t>899424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>941128</t>
+          <t>941230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46922</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77296</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>36525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65855</t>
+          <t>64665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>129842</t>
+          <t>129868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>300969</t>
+          <t>302068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>316196</t>
+          <t>316356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>314858</t>
+          <t>314330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>331776</t>
+          <t>331169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>622755</t>
+          <t>621417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>644478</t>
+          <t>644084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42311</t>
+          <t>43649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>351537</t>
+          <t>352168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>367985</t>
+          <t>368310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>367782</t>
+          <t>367549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381238</t>
+          <t>381388</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>725034</t>
+          <t>725572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>745747</t>
+          <t>745528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22445</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20265</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36995</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>195968</t>
+          <t>196468</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208709</t>
+          <t>208557</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194513</t>
+          <t>195394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>211316</t>
+          <t>211344</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397288</t>
+          <t>396291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416717</t>
+          <t>416236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34921</t>
+          <t>35918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>249603</t>
+          <t>248537</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>266079</t>
+          <t>265971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>258435</t>
+          <t>259590</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>272358</t>
+          <t>272401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>514775</t>
+          <t>513317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>535479</t>
+          <t>535252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38259</t>
+          <t>39717</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>605656</t>
+          <t>605673</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>632559</t>
+          <t>631838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>631853</t>
+          <t>631607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>657815</t>
+          <t>658653</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1248066</t>
+          <t>1248858</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1283558</t>
+          <t>1286830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29316</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56219</t>
+          <t>56202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57959</t>
+          <t>58205</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>64856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103620</t>
+          <t>102828</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>741498</t>
+          <t>742346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>764132</t>
+          <t>764717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>784093</t>
+          <t>785983</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>805713</t>
+          <t>806411</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1534837</t>
+          <t>1535768</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1565423</t>
+          <t>1565900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>67183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3161665</t>
+          <t>3165996</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3227948</t>
+          <t>3224637</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3313344</t>
+          <t>3314081</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3374125</t>
+          <t>3372541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6498776</t>
+          <t>6501487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6586109</t>
+          <t>6583665</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>197917</t>
+          <t>201228</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>264200</t>
+          <t>259869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>178260</t>
+          <t>179844</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>239041</t>
+          <t>238304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>392141</t>
+          <t>394585</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>479474</t>
+          <t>476763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241161</t>
+          <t>239447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>265680</t>
+          <t>266190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251944</t>
+          <t>254024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>272271</t>
+          <t>272333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>503104</t>
+          <t>501817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>533647</t>
+          <t>534008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27021</t>
+          <t>26511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51540</t>
+          <t>53254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>34679</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47757</t>
+          <t>47396</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78300</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>408908</t>
+          <t>411183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>442547</t>
+          <t>442923</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>455760</t>
+          <t>455926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>483090</t>
+          <t>483566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>876806</t>
+          <t>876784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>920130</t>
+          <t>919169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92584</t>
+          <t>90309</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67324</t>
+          <t>67158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104446</t>
+          <t>105407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147770</t>
+          <t>147792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>298541</t>
+          <t>298227</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311884</t>
+          <t>311949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>324235</t>
+          <t>324445</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>334311</t>
+          <t>334286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>627469</t>
+          <t>626652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>643242</t>
+          <t>643754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26436</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>314891</t>
+          <t>316032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>339945</t>
+          <t>340567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>348785</t>
+          <t>348436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>369771</t>
+          <t>369821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>672779</t>
+          <t>671042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>704674</t>
+          <t>704890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30019</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55073</t>
+          <t>53932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>37966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51692</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83587</t>
+          <t>85324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>201154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210236</t>
+          <t>210246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>211065</t>
+          <t>211415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217778</t>
+          <t>217767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>416142</t>
+          <t>416634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>427181</t>
+          <t>427333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214574</t>
+          <t>213608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237082</t>
+          <t>236924</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>243448</t>
+          <t>242652</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>259612</t>
+          <t>259647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>464757</t>
+          <t>461511</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>492743</t>
+          <t>492196</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48549</t>
+          <t>49515</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>44042</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71481</t>
+          <t>74727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586593</t>
+          <t>585422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>615562</t>
+          <t>615475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>615447</t>
+          <t>615970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>646235</t>
+          <t>645951</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1212479</t>
+          <t>1212966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1255593</t>
+          <t>1253529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39048</t>
+          <t>39135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68017</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73761</t>
+          <t>73238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>88225</t>
+          <t>90289</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>131339</t>
+          <t>130852</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>741647</t>
+          <t>740431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>762561</t>
+          <t>761230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>792881</t>
+          <t>793518</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>811523</t>
+          <t>811645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1540915</t>
+          <t>1541919</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1568916</t>
+          <t>1569369</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33992</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61993</t>
+          <t>60989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3074831</t>
+          <t>3074343</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3142986</t>
+          <t>3139692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3301378</t>
+          <t>3301831</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3359736</t>
+          <t>3356938</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6397489</t>
+          <t>6394732</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6478012</t>
+          <t>6479156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>244462</t>
+          <t>247756</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>312617</t>
+          <t>313105</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>181839</t>
+          <t>184637</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>240197</t>
+          <t>239744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>451011</t>
+          <t>449867</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>531534</t>
+          <t>534291</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>295390</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285763</t>
+          <t>290124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>302090</t>
+          <t>307999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>270490</t>
+          <t>293528</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>261454</t>
+          <t>283111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277046</t>
+          <t>300519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>565879</t>
+          <t>594409</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>552081</t>
+          <t>580418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>575171</t>
+          <t>605667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>22533</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>32950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35198</t>
+          <t>40497</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>54488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368862</t>
+          <t>380580</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342881</t>
+          <t>356951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>394865</t>
+          <t>405139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>406280</t>
+          <t>434141</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>389648</t>
+          <t>415987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>423028</t>
+          <t>451576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>775142</t>
+          <t>814721</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>748702</t>
+          <t>781935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>808002</t>
+          <t>842027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>149528</t>
+          <t>150067</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123525</t>
+          <t>125508</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175509</t>
+          <t>173696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108689</t>
+          <t>112353</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>94918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125321</t>
+          <t>130507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>258217</t>
+          <t>262420</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225357</t>
+          <t>235114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284657</t>
+          <t>295206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>306965</t>
+          <t>305368</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>299907</t>
+          <t>298149</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>311028</t>
+          <t>309764</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>325003</t>
+          <t>332016</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>315276</t>
+          <t>322816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>332697</t>
+          <t>339672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>631968</t>
+          <t>637385</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620504</t>
+          <t>624550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>640519</t>
+          <t>646512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24125</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33852</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>33210</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>47825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>288964</t>
+          <t>340553</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>272456</t>
+          <t>321859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298553</t>
+          <t>353181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382614</t>
+          <t>390134</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234718</t>
+          <t>379637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>452308</t>
+          <t>399194</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>671578</t>
+          <t>730687</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>485767</t>
+          <t>710024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>739862</t>
+          <t>746814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>51286</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>93104</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>22767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>241000</t>
+          <t>42324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>116696</t>
+          <t>64420</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>48293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302507</t>
+          <t>85083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,27 +12069,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>200747</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170108</t>
+          <t>195308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>176951</t>
+          <t>203604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>202901</t>
+          <t>222282</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>196251</t>
+          <t>217207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205925</t>
+          <t>224720</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>377666</t>
+          <t>423028</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370995</t>
+          <t>416094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>381831</t>
+          <t>426963</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -12182,22 +12182,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16021</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>236692</t>
+          <t>236302</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>225700</t>
+          <t>226054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>245559</t>
+          <t>245686</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>238127</t>
+          <t>243716</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>230779</t>
+          <t>236204</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243315</t>
+          <t>249285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>480017</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>460433</t>
+          <t>467876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>486093</t>
+          <t>491953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43936</t>
+          <t>44653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>51874</t>
+          <t>54440</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40599</t>
+          <t>42504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>562430</t>
+          <t>648977</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>542079</t>
+          <t>627817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579000</t>
+          <t>665194</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>781331</t>
+          <t>685985</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>753375</t>
+          <t>669120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>819355</t>
+          <t>701061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1343761</t>
+          <t>1334962</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1309182</t>
+          <t>1309091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1391831</t>
+          <t>1360730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>61849</t>
+          <t>70710</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45279</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82200</t>
+          <t>91870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67934</t>
+          <t>86072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>70996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95890</t>
+          <t>102937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>129783</t>
+          <t>156782</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81713</t>
+          <t>131014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>164362</t>
+          <t>182653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>813405</t>
+          <t>666129</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>764469</t>
+          <t>642836</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>878458</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,22 +13133,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>621940</t>
+          <t>720879</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>606608</t>
+          <t>702610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>636900</t>
+          <t>737864</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1435347</t>
+          <t>1387008</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1388631</t>
+          <t>1359134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1515604</t>
+          <t>1412363</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>115315</t>
+          <t>131943</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50262</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>164251</t>
+          <t>155236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>95791</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80831</t>
+          <t>93467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111123</t>
+          <t>128721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>211105</t>
+          <t>242395</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130848</t>
+          <t>217040</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>257821</t>
+          <t>270269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3047473</t>
+          <t>3079536</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2989897</t>
+          <t>3032838</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3136156</t>
+          <t>3124665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3228685</t>
+          <t>3322683</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3024967</t>
+          <t>3286012</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3314975</t>
+          <t>3355599</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6276158</t>
+          <t>6402219</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6055024</t>
+          <t>6349366</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6388820</t>
+          <t>6455660</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>412344</t>
+          <t>453226</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>323661</t>
+          <t>408097</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>469920</t>
+          <t>499924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>433089</t>
+          <t>412177</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>346799</t>
+          <t>379261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>636807</t>
+          <t>448848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>845433</t>
+          <t>865403</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>732771</t>
+          <t>811962</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1066567</t>
+          <t>918256</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3661774</t>
+          <t>3734860</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7121591</t>
+          <t>7267622</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
